--- a/App/Data/figure_titles.xlsx
+++ b/App/Data/figure_titles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gio\Desktop\Documents\I2D2\I2D2 Dashboard\IDD_Dashboards\IDD_Dashboard_App_Dev\App\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B29B1DD-23F5-4FB7-B032-185BA997ABEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0574C863-96D8-45E3-A09D-DC5DEC047729}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="575">
   <si>
     <t>Dimension</t>
   </si>
@@ -1741,6 +1741,15 @@
   </si>
   <si>
     <t>No info</t>
+  </si>
+  <si>
+    <t>Mothers Receiving WIC Prior to Child's Birth</t>
+  </si>
+  <si>
+    <t># of mothers receiving WIC</t>
+  </si>
+  <si>
+    <t>Percentage of mothers receiving WIC</t>
   </si>
 </sst>
 </file>
@@ -2309,7 +2318,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -2346,6 +2355,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2392,13 +2404,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment horizontal="right"/>
     </dxf>
@@ -2752,6 +2757,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3935,7 +3947,7 @@
     <dataField name="Percent of Indicators" fld="10" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="9"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="11">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -3944,10 +3956,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="9">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3957,7 +3969,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="7">
       <pivotArea dataOnly="0" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3967,26 +3979,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="6">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="4">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3996,7 +4008,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -4013,8 +4025,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC23B1C9-B5D3-4474-9D5F-318B476A3360}" name="Table1" displayName="Table1" ref="A1:Q149" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" tableBorderDxfId="43">
-  <autoFilter ref="A1:Q149" xr:uid="{0AC4A32E-D3F5-43D3-8546-EA9B69D2C5FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC23B1C9-B5D3-4474-9D5F-318B476A3360}" name="Table1" displayName="Table1" ref="A1:Q150" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" tableBorderDxfId="43">
+  <autoFilter ref="A1:Q150" xr:uid="{0AC4A32E-D3F5-43D3-8546-EA9B69D2C5FA}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{350E42F7-F668-44CF-AC33-D55A845345D3}" name="FigureID" dataDxfId="42">
       <calculatedColumnFormula>_xlfn.CONCAT(VLOOKUP(_xlfn.CONCAT(Table1[[#This Row],[Dimension]],Table1[[#This Row],[Measure]],Table1[[#This Row],[Indicator]]),IndicatorType[],2,FALSE),".00",Table1[[#This Row],[Figure  ]])</calculatedColumnFormula>
@@ -4041,27 +4053,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{294150C7-1BE3-4AD2-813C-6F857E4331FA}" name="IndicatorType" displayName="IndicatorType" ref="A1:K42" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{294150C7-1BE3-4AD2-813C-6F857E4331FA}" name="IndicatorType" displayName="IndicatorType" ref="A1:K42" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A1:K42" xr:uid="{0AC4A32E-D3F5-43D3-8546-EA9B69D2C5FA}"/>
   <sortState ref="A2:J42">
     <sortCondition ref="B1:B42"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8BB510C9-3856-4776-9748-95E49C312F38}" name="VLUP" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{8BB510C9-3856-4776-9748-95E49C312F38}" name="VLUP" dataDxfId="21">
       <calculatedColumnFormula>_xlfn.CONCAT(IndicatorType[[#This Row],[Dimension]],IndicatorType[[#This Row],[Measure]],IndicatorType[[#This Row],[Indicator]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9546C1A1-578E-4D17-9635-40FDF82CD4C4}" name="IndicatorID" dataDxfId="21">
+    <tableColumn id="7" xr3:uid="{9546C1A1-578E-4D17-9635-40FDF82CD4C4}" name="IndicatorID" dataDxfId="20">
       <calculatedColumnFormula>UPPER(_xlfn.CONCAT(IndicatorType[[#This Row],[CodeDim]],".",IndicatorType[[#This Row],[CodeMsr]],".",IndicatorType[[#This Row],[CodeInd]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{9187F260-66D1-4B5A-9D69-EC2E8C75062F}" name="CodeDim" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{079147DF-C18C-4615-BD67-DD8E341D022D}" name="CodeMsr" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{658FF864-2269-4908-9945-0821F8B1030B}" name="CodeInd" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{58FC67EB-2F1D-42AF-A890-570A48CFF751}" name="Dimension" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{0C471E0E-AA62-4645-8064-4F59A45822C4}" name="Measure" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{B97F0656-BF62-4E17-96F1-A6142ADCAB0A}" name="Indicator" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{E0814273-C288-4DF2-8C90-905AD0D5AEA4}" name="Data Type" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{3F2886C1-1086-4B66-BECD-85DAC7F72803}" name="Comments" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{585F44AF-4E4B-4CDD-A743-66562926C15A}" name="ComputedBy" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{9187F260-66D1-4B5A-9D69-EC2E8C75062F}" name="CodeDim" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{079147DF-C18C-4615-BD67-DD8E341D022D}" name="CodeMsr" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{658FF864-2269-4908-9945-0821F8B1030B}" name="CodeInd" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{58FC67EB-2F1D-42AF-A890-570A48CFF751}" name="Dimension" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{0C471E0E-AA62-4645-8064-4F59A45822C4}" name="Measure" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{B97F0656-BF62-4E17-96F1-A6142ADCAB0A}" name="Indicator" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{E0814273-C288-4DF2-8C90-905AD0D5AEA4}" name="Data Type" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{3F2886C1-1086-4B66-BECD-85DAC7F72803}" name="Comments" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{585F44AF-4E4B-4CDD-A743-66562926C15A}" name="ComputedBy" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4364,7 +4376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q149"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" style="7" customWidth="1"/>
@@ -11271,6 +11283,52 @@
       <c r="Q149" s="2" t="s">
         <v>325</v>
       </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150" s="28" t="str">
+        <f>_xlfn.CONCAT(VLOOKUP(_xlfn.CONCAT(Table1[[#This Row],[Dimension]],Table1[[#This Row],[Measure]],Table1[[#This Row],[Indicator]]),IndicatorType[],2,FALSE),".00",Table1[[#This Row],[Figure  ]])</f>
+        <v>SRV.SER.WIC.004</v>
+      </c>
+      <c r="B150" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="C150" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26">
+        <v>4</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="O150" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P150" s="27"/>
+      <c r="Q150" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12775,7 +12833,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:K42">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$K2="Gio"</formula>
     </cfRule>
   </conditionalFormatting>
